--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T10:29:33+00:00</t>
+    <t>2026-03-01T15:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T15:46:45+00:00</t>
+    <t>2026-03-02T16:20:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T16:20:44+00:00</t>
+    <t>2026-03-02T17:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T17:40:54+00:00</t>
+    <t>2026-03-03T16:09:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T16:09:57+00:00</t>
+    <t>2026-03-03T18:16:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T18:16:34+00:00</t>
+    <t>2026-03-03T20:10:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T20:10:31+00:00</t>
+    <t>2026-03-24T11:22:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T11:22:25+00:00</t>
+    <t>2026-03-27T21:20:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -103,12 +103,6 @@
   </si>
   <si>
     <t>Concept</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>minute</t>
   </si>
   <si>
     <t>{finding}</t>
@@ -398,7 +392,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -431,26 +425,18 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T21:20:49+00:00</t>
+    <t>2026-03-29T11:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:39:37+00:00</t>
+    <t>2026-03-29T11:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:44:39+00:00</t>
+    <t>2026-04-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T14:50:23+00:00</t>
+    <t>2026-05-18T08:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T08:38:27+00:00</t>
+    <t>2026-05-18T10:23:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T10:23:40+00:00</t>
+    <t>2026-06-01T14:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:49:28+00:00</t>
+    <t>2026-06-03T09:07:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:07:40+00:00</t>
+    <t>2026-06-03T10:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T10:15:52+00:00</t>
+    <t>2026-06-16T06:28:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T06:28:21+00:00</t>
+    <t>2026-06-18T08:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:24:24+00:00</t>
+    <t>2026-06-18T13:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:26:12+00:00</t>
+    <t>2026-06-22T11:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T11:44:44+00:00</t>
+    <t>2026-06-22T12:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:35:22+00:00</t>
+    <t>2026-06-22T13:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:57:07+00:00</t>
+    <t>2026-06-22T14:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:44:05+00:00</t>
+    <t>2026-06-24T07:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:32:55+00:00</t>
+    <t>2026-06-24T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:07:10+00:00</t>
+    <t>2026-06-24T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:18:54+00:00</t>
+    <t>2026-06-29T10:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-units.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
